--- a/tasks/finalpool/pw-sf-wc-reconciliation-excel-word/groundtruth_workspace/Wc_Reconciliation_Report.xlsx
+++ b/tasks/finalpool/pw-sf-wc-reconciliation-excel-word/groundtruth_workspace/Wc_Reconciliation_Report.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,26 +27,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -61,9 +48,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,33 +415,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Order_Count</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Market_Size_M</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Market_Penetration_Pct</t>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Our_Order_Count</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Industry_Avg_Order_Count</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Order_Gap</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Our_Revenue</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Industry_Avg_Revenue</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Revenue_Gap</t>
         </is>
       </c>
     </row>
@@ -469,13 +465,19 @@
         <v>4198</v>
       </c>
       <c r="C2" t="n">
+        <v>4500</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-302</v>
+      </c>
+      <c r="E2" t="n">
         <v>642644.8100000001</v>
       </c>
-      <c r="D2" t="n">
-        <v>439</v>
-      </c>
-      <c r="E2" t="n">
-        <v>146388.3</v>
+      <c r="F2" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-57355.19</v>
       </c>
     </row>
     <row r="3">
@@ -488,13 +490,19 @@
         <v>4100</v>
       </c>
       <c r="C3" t="n">
+        <v>4300</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E3" t="n">
         <v>648798.47</v>
       </c>
-      <c r="D3" t="n">
-        <v>339</v>
-      </c>
-      <c r="E3" t="n">
-        <v>191386</v>
+      <c r="F3" t="n">
+        <v>680000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-31201.53</v>
       </c>
     </row>
     <row r="4">
@@ -507,13 +515,19 @@
         <v>3697</v>
       </c>
       <c r="C4" t="n">
+        <v>3800</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-103</v>
+      </c>
+      <c r="E4" t="n">
         <v>549129.15</v>
       </c>
-      <c r="D4" t="n">
-        <v>453</v>
-      </c>
-      <c r="E4" t="n">
-        <v>121220.6</v>
+      <c r="F4" t="n">
+        <v>580000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-30870.85</v>
       </c>
     </row>
     <row r="5">
@@ -526,13 +540,19 @@
         <v>3872</v>
       </c>
       <c r="C5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-128</v>
+      </c>
+      <c r="E5" t="n">
         <v>602107.55</v>
       </c>
-      <c r="D5" t="n">
-        <v>421</v>
-      </c>
-      <c r="E5" t="n">
-        <v>143018.4</v>
+      <c r="F5" t="n">
+        <v>620000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-17892.45</v>
       </c>
     </row>
     <row r="6">
@@ -545,13 +565,19 @@
         <v>4133</v>
       </c>
       <c r="C6" t="n">
+        <v>4250</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-117</v>
+      </c>
+      <c r="E6" t="n">
         <v>606318.35</v>
       </c>
-      <c r="D6" t="n">
-        <v>463</v>
-      </c>
-      <c r="E6" t="n">
-        <v>130954.3</v>
+      <c r="F6" t="n">
+        <v>650000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-43681.65</v>
       </c>
     </row>
   </sheetData>
@@ -565,16 +591,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -613,11 +639,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Avg_Market_Penetration</t>
+          <t>Avg_Order_Gap</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>146593.5</v>
+        <v>-170</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Avg_Revenue_Gap</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-36200.33</v>
       </c>
     </row>
   </sheetData>
@@ -631,21 +667,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
@@ -657,12 +693,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Expand presence</t>
+          <t>Expand presence to close revenue gap</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
     </row>
@@ -672,10 +708,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optimize operations</t>
+          <t>Optimize operations to address order gap</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Investigate underperformance</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
